--- a/samples/Q_无形资产明细表.xlsx
+++ b/samples/Q_无形资产明细表.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,168 +438,332 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>资产编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>资产名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>资产类别</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>取得日期</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>原值</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>累计摊销</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>净值</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>本年摊销</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>摊销年限</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>取得日期</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>本月摊销</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>剩余月数</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>专利权A</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>900000</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>10年</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>2020-01</t>
+          <t>WX-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>渝北工业园区土地使用权</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>土地使用权</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2018-01-01</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>560000</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>2240000</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>4667</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>490</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>工业用地50年</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>专利权B</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>800000</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>240000</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>560000</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>80000</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>10年</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>2021-06</t>
+          <t>WX-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>智能制造专利</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>专利权</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>4167</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>发明专利</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>管理软件</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>700000</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>120000</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10年</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2022-03</t>
+          <t>WX-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>MES生产管理系统</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>软件</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>550000</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>本年新增ERP模块</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>专利权C(本期新增)</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
+          <t>WX-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>旧财务软件</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>软件</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>200000</v>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>180000</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5年</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2024-07</t>
+      <c r="F5" s="3" t="n">
+        <v>140000</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>3333</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>停用</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>已摊销完毕，关注是否继续使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WX-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>新型传感器专利</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>专利权</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>8333</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>191667</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1667</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>在用</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>本年新增专利，关注减值测试</t>
         </is>
       </c>
     </row>
